--- a/forms/CHECKLIST.xlsx
+++ b/forms/CHECKLIST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LENOVOT520/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\backkkk\Monitor\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B1CC7F-CC0D-224D-BFD1-C7AAC19A56F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C08D52-4FA8-4667-9813-F42B3BF19C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="22840" windowHeight="16140" xr2:uid="{3F82D4E0-9CC1-4A6F-9DB3-71E7747E4309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{3F82D4E0-9CC1-4A6F-9DB3-71E7747E4309}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -925,7 +926,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -966,7 +967,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -987,6 +987,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1259,9 +1271,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1299,7 +1311,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1405,7 +1417,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1547,7 +1559,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1559,82 +1571,82 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:O70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="3.83203125" customWidth="1"/>
-    <col min="4" max="4" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="3.85546875" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="21.1640625" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" customWidth="1"/>
-    <col min="8" max="8" width="3.83203125" customWidth="1"/>
-    <col min="9" max="9" width="4.83203125" customWidth="1"/>
-    <col min="10" max="10" width="4.1640625" customWidth="1"/>
-    <col min="11" max="11" width="21.5" customWidth="1"/>
-    <col min="12" max="12" width="4.33203125" customWidth="1"/>
-    <col min="13" max="13" width="4.1640625" customWidth="1"/>
-    <col min="14" max="14" width="5.1640625" customWidth="1"/>
-    <col min="15" max="15" width="4.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" customWidth="1"/>
+    <col min="7" max="7" width="4.28515625" customWidth="1"/>
+    <col min="8" max="8" width="3.85546875" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" customWidth="1"/>
+    <col min="10" max="10" width="4.140625" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="4.140625" customWidth="1"/>
+    <col min="14" max="14" width="5.140625" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="35" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H3" s="10"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
-      <c r="O3" s="36" t="s">
+      <c r="O3" s="35" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
-      <c r="O4" s="36" t="s">
+      <c r="O4" s="35" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="39" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
       <c r="O5" s="10"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
       <c r="O6" s="10"/>
     </row>
-    <row r="7" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>96</v>
       </c>
@@ -1653,15 +1665,15 @@
       </c>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
-      <c r="K8" s="30" t="s">
+      <c r="K8" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="L8" s="31"/>
-      <c r="M8" s="35"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="34"/>
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>102</v>
       </c>
@@ -1678,7 +1690,7 @@
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
-      <c r="K9" s="34" t="s">
+      <c r="K9" s="33" t="s">
         <v>163</v>
       </c>
       <c r="L9" s="22"/>
@@ -1686,16 +1698,16 @@
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
       <c r="F10" s="14" t="s">
         <v>92</v>
       </c>
@@ -1703,20 +1715,20 @@
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="32"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="14"/>
-      <c r="M10" s="33"/>
+      <c r="M10" s="32"/>
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
@@ -1728,7 +1740,7 @@
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>93</v>
       </c>
@@ -1757,8 +1769,8 @@
       <c r="N12" s="14"/>
       <c r="O12" s="14"/>
     </row>
-    <row r="13" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>0</v>
       </c>
@@ -1805,7 +1817,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>1</v>
       </c>
@@ -1828,7 +1840,7 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>2</v>
       </c>
@@ -1851,7 +1863,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
@@ -1874,7 +1886,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
@@ -1897,7 +1909,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
@@ -1920,7 +1932,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -1943,7 +1955,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -1966,7 +1978,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +2001,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>9</v>
       </c>
@@ -2012,7 +2024,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -2035,7 +2047,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -2058,7 +2070,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>147</v>
       </c>
@@ -2081,7 +2093,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
@@ -2104,7 +2116,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>13</v>
       </c>
@@ -2127,7 +2139,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>116</v>
       </c>
@@ -2150,7 +2162,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>14</v>
       </c>
@@ -2173,7 +2185,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>15</v>
       </c>
@@ -2196,7 +2208,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>16</v>
       </c>
@@ -2219,7 +2231,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>17</v>
       </c>
@@ -2242,7 +2254,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>18</v>
       </c>
@@ -2265,7 +2277,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>117</v>
       </c>
@@ -2288,7 +2300,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>19</v>
       </c>
@@ -2311,7 +2323,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>20</v>
       </c>
@@ -2332,7 +2344,7 @@
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>21</v>
       </c>
@@ -2353,7 +2365,7 @@
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -2376,7 +2388,7 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>22</v>
       </c>
@@ -2399,7 +2411,7 @@
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>123</v>
       </c>
@@ -2422,7 +2434,7 @@
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>23</v>
       </c>
@@ -2445,7 +2457,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -2468,7 +2480,7 @@
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>119</v>
       </c>
@@ -2491,7 +2503,7 @@
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>25</v>
       </c>
@@ -2514,7 +2526,7 @@
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>26</v>
       </c>
@@ -2535,7 +2547,7 @@
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>27</v>
       </c>
@@ -2556,7 +2568,7 @@
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>28</v>
       </c>
@@ -2577,7 +2589,7 @@
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>29</v>
       </c>
@@ -2598,7 +2610,7 @@
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>30</v>
       </c>
@@ -2621,7 +2633,7 @@
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>120</v>
       </c>
@@ -2644,7 +2656,7 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>121</v>
       </c>
@@ -2667,7 +2679,7 @@
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>31</v>
       </c>
@@ -2690,7 +2702,7 @@
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>32</v>
       </c>
@@ -2713,7 +2725,7 @@
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>33</v>
       </c>
@@ -2736,7 +2748,7 @@
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>34</v>
       </c>
@@ -2759,7 +2771,7 @@
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>35</v>
       </c>
@@ -2780,7 +2792,7 @@
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>36</v>
       </c>
@@ -2801,7 +2813,7 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>37</v>
       </c>
@@ -2822,7 +2834,7 @@
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>38</v>
       </c>
@@ -2843,7 +2855,7 @@
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
         <v>112</v>
       </c>
@@ -2864,8 +2876,12 @@
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A62" s="28"/>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="39"/>
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
       <c r="F62" s="2" t="s">
         <v>69</v>
       </c>
@@ -2879,8 +2895,12 @@
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A63" s="28"/>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="39"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="40"/>
       <c r="F63" s="2" t="s">
         <v>70</v>
       </c>
@@ -2894,24 +2914,36 @@
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A64" s="28"/>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="39"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
       <c r="O64" s="19"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A65" s="28"/>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="39"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
       <c r="O65" s="20"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A66" s="28"/>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="39"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
       <c r="O66" s="20"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A67" s="6"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="41"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
       <c r="F67" s="14"/>
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
@@ -2923,29 +2955,30 @@
       <c r="N67" s="14"/>
       <c r="O67" s="21"/>
     </row>
-    <row r="68" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A68" s="29" t="s">
+    <row r="68" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A68" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="28" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
+    <row r="69" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A69" s="28" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A70" s="29" t="s">
+    <row r="70" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A70" s="28" t="s">
         <v>160</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B5:J6"/>
+    <mergeCell ref="A62:E67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" copies="20" r:id="rId1"/>
